--- a/artfynd/A 20285-2024 artfynd.xlsx
+++ b/artfynd/A 20285-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119676908</v>
+        <v>119676911</v>
       </c>
       <c r="B6" t="n">
-        <v>57326</v>
+        <v>96862</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861559</v>
+        <v>861642</v>
       </c>
       <c r="R6" t="n">
-        <v>7504017</v>
+        <v>7504030</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119676911</v>
+        <v>119676908</v>
       </c>
       <c r="B7" t="n">
-        <v>96862</v>
+        <v>57326</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861642</v>
+        <v>861559</v>
       </c>
       <c r="R7" t="n">
-        <v>7504030</v>
+        <v>7504017</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 20285-2024 artfynd.xlsx
+++ b/artfynd/A 20285-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119676912</v>
+        <v>119676908</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>861220</v>
+        <v>861559</v>
       </c>
       <c r="R2" t="n">
-        <v>7504047</v>
+        <v>7504017</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119676896</v>
+        <v>119676912</v>
       </c>
       <c r="B3" t="n">
-        <v>90905</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861281</v>
+        <v>861220</v>
       </c>
       <c r="R3" t="n">
-        <v>7504099</v>
+        <v>7504047</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119676913</v>
+        <v>119676905</v>
       </c>
       <c r="B4" t="n">
-        <v>82305</v>
+        <v>57326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861572</v>
+        <v>861272</v>
       </c>
       <c r="R4" t="n">
-        <v>7504061</v>
+        <v>7504005</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119676906</v>
+        <v>119676913</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>82305</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861381</v>
+        <v>861572</v>
       </c>
       <c r="R5" t="n">
-        <v>7503945</v>
+        <v>7504061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119676911</v>
+        <v>119676896</v>
       </c>
       <c r="B6" t="n">
-        <v>96862</v>
+        <v>90905</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861642</v>
+        <v>861281</v>
       </c>
       <c r="R6" t="n">
-        <v>7504030</v>
+        <v>7504099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119676908</v>
+        <v>119676901</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861559</v>
+        <v>861218</v>
       </c>
       <c r="R7" t="n">
-        <v>7504017</v>
+        <v>7504033</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119676902</v>
+        <v>119676906</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>57326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861281</v>
+        <v>861381</v>
       </c>
       <c r="R8" t="n">
-        <v>7504099</v>
+        <v>7503945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119676901</v>
+        <v>119676897</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>57326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861218</v>
+        <v>861357</v>
       </c>
       <c r="R9" t="n">
-        <v>7504033</v>
+        <v>7503964</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119676897</v>
+        <v>119676911</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>96862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>861357</v>
+        <v>861642</v>
       </c>
       <c r="R10" t="n">
-        <v>7503964</v>
+        <v>7504030</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119676905</v>
+        <v>119676902</v>
       </c>
       <c r="B11" t="n">
-        <v>57326</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>861272</v>
+        <v>861281</v>
       </c>
       <c r="R11" t="n">
-        <v>7504005</v>
+        <v>7504099</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 20285-2024 artfynd.xlsx
+++ b/artfynd/A 20285-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119676908</v>
+        <v>119676905</v>
       </c>
       <c r="B2" t="n">
         <v>57326</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>861559</v>
+        <v>861272</v>
       </c>
       <c r="R2" t="n">
-        <v>7504017</v>
+        <v>7504005</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119676912</v>
+        <v>119676896</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>90905</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861220</v>
+        <v>861281</v>
       </c>
       <c r="R3" t="n">
-        <v>7504047</v>
+        <v>7504099</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119676905</v>
+        <v>119676906</v>
       </c>
       <c r="B4" t="n">
         <v>57326</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861272</v>
+        <v>861381</v>
       </c>
       <c r="R4" t="n">
-        <v>7504005</v>
+        <v>7503945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119676913</v>
+        <v>119676912</v>
       </c>
       <c r="B5" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861572</v>
+        <v>861220</v>
       </c>
       <c r="R5" t="n">
-        <v>7504061</v>
+        <v>7504047</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119676896</v>
+        <v>119676901</v>
       </c>
       <c r="B6" t="n">
-        <v>90905</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861281</v>
+        <v>861218</v>
       </c>
       <c r="R6" t="n">
-        <v>7504099</v>
+        <v>7504033</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119676901</v>
+        <v>119676911</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
+        <v>96862</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861218</v>
+        <v>861642</v>
       </c>
       <c r="R7" t="n">
-        <v>7504033</v>
+        <v>7504030</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119676906</v>
+        <v>119676902</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
+        <v>90562</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861381</v>
+        <v>861281</v>
       </c>
       <c r="R8" t="n">
-        <v>7503945</v>
+        <v>7504099</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119676911</v>
+        <v>119676908</v>
       </c>
       <c r="B10" t="n">
-        <v>96862</v>
+        <v>57326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>861642</v>
+        <v>861559</v>
       </c>
       <c r="R10" t="n">
-        <v>7504030</v>
+        <v>7504017</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119676902</v>
+        <v>119676913</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>861281</v>
+        <v>861572</v>
       </c>
       <c r="R11" t="n">
-        <v>7504099</v>
+        <v>7504061</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 20285-2024 artfynd.xlsx
+++ b/artfynd/A 20285-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119676896</v>
+        <v>119676912</v>
       </c>
       <c r="B3" t="n">
-        <v>90905</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861281</v>
+        <v>861220</v>
       </c>
       <c r="R3" t="n">
-        <v>7504099</v>
+        <v>7504047</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119676906</v>
+        <v>119676908</v>
       </c>
       <c r="B4" t="n">
         <v>57326</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861381</v>
+        <v>861559</v>
       </c>
       <c r="R4" t="n">
-        <v>7503945</v>
+        <v>7504017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119676912</v>
+        <v>119676913</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861220</v>
+        <v>861572</v>
       </c>
       <c r="R5" t="n">
-        <v>7504047</v>
+        <v>7504061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119676901</v>
+        <v>119676902</v>
       </c>
       <c r="B6" t="n">
         <v>90562</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861218</v>
+        <v>861281</v>
       </c>
       <c r="R6" t="n">
-        <v>7504033</v>
+        <v>7504099</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119676911</v>
+        <v>119676897</v>
       </c>
       <c r="B7" t="n">
-        <v>96862</v>
+        <v>57326</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861642</v>
+        <v>861357</v>
       </c>
       <c r="R7" t="n">
-        <v>7504030</v>
+        <v>7503964</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119676902</v>
+        <v>119676906</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
+        <v>57326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861281</v>
+        <v>861381</v>
       </c>
       <c r="R8" t="n">
-        <v>7504099</v>
+        <v>7503945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119676897</v>
+        <v>119676896</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>90905</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861357</v>
+        <v>861281</v>
       </c>
       <c r="R9" t="n">
-        <v>7503964</v>
+        <v>7504099</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119676908</v>
+        <v>119676911</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
+        <v>96862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>861559</v>
+        <v>861642</v>
       </c>
       <c r="R10" t="n">
-        <v>7504017</v>
+        <v>7504030</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119676913</v>
+        <v>119676901</v>
       </c>
       <c r="B11" t="n">
-        <v>82305</v>
+        <v>90562</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>861572</v>
+        <v>861218</v>
       </c>
       <c r="R11" t="n">
-        <v>7504061</v>
+        <v>7504033</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
